--- a/data/trans_orig/P71_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>82294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115010</t>
+          <t>115515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141487</t>
+          <t>141629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188411</t>
+          <t>187102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404466</t>
+          <t>405143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433852</t>
+          <t>434068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345017</t>
+          <t>344512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>378005</t>
+          <t>377733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757437</t>
+          <t>758746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>804361</t>
+          <t>804219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106468</t>
+          <t>105270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148556</t>
+          <t>144884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108524</t>
+          <t>110700</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150490</t>
+          <t>152209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228401</t>
+          <t>226153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288364</t>
+          <t>287009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583107</t>
+          <t>586779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>625195</t>
+          <t>626393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463290</t>
+          <t>461571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505256</t>
+          <t>503080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1057079</t>
+          <t>1058434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1117042</t>
+          <t>1119290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77054</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114328</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152600</t>
+          <t>150654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199654</t>
+          <t>195683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>238207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297360</t>
+          <t>298620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520806</t>
+          <t>521806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>558080</t>
+          <t>557798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478073</t>
+          <t>482044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525127</t>
+          <t>527073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015501</t>
+          <t>1014241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073999</t>
+          <t>1074654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65562</t>
+          <t>65528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101396</t>
+          <t>100692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112367</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153317</t>
+          <t>154020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191114</t>
+          <t>192279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243205</t>
+          <t>242044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414861</t>
+          <t>415565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450695</t>
+          <t>450729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352103</t>
+          <t>351400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>393053</t>
+          <t>391280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>778472</t>
+          <t>779633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830563</t>
+          <t>829398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73162</t>
+          <t>72847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105100</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97657</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132633</t>
+          <t>132277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180275</t>
+          <t>176744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228099</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271050</t>
+          <t>271821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302988</t>
+          <t>303303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264270</t>
+          <t>264626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299246</t>
+          <t>300493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>544954</t>
+          <t>547874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>592778</t>
+          <t>596309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53482</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80661</t>
+          <t>82633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117393</t>
+          <t>119062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151843</t>
+          <t>151768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179989</t>
+          <t>180606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224863</t>
+          <t>224003</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202101</t>
+          <t>200129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229280</t>
+          <t>228523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180263</t>
+          <t>180338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214713</t>
+          <t>213044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390005</t>
+          <t>390865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434879</t>
+          <t>434262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>50446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76067</t>
+          <t>76793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116413</t>
+          <t>119527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156711</t>
+          <t>155729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177407</t>
+          <t>179893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224584</t>
+          <t>223629</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126975</t>
+          <t>126249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152856</t>
+          <t>152596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172294</t>
+          <t>173276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212592</t>
+          <t>209478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307464</t>
+          <t>308419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354641</t>
+          <t>352155</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2604047</t>
+          <t>2603359</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2694424</t>
+          <t>2687893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2337256</t>
+          <t>2336996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2441934</t>
+          <t>2441239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4975929</t>
+          <t>4968419</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5115863</t>
+          <t>5102619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112453</t>
+          <t>109456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152486</t>
+          <t>149136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91110</t>
+          <t>93575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130575</t>
+          <t>130031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214053</t>
+          <t>215174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267108</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>298767</t>
+          <t>302117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338800</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298725</t>
+          <t>299269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338190</t>
+          <t>335725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>613445</t>
+          <t>613042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666500</t>
+          <t>665379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182135</t>
+          <t>181749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228299</t>
+          <t>229818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182004</t>
+          <t>183140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229708</t>
+          <t>232414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381513</t>
+          <t>374685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446087</t>
+          <t>442962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456894</t>
+          <t>455375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503058</t>
+          <t>503444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>380547</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428251</t>
+          <t>427115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849362</t>
+          <t>852487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>913936</t>
+          <t>920764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211092</t>
+          <t>214822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>264093</t>
+          <t>263263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225749</t>
+          <t>224661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>277289</t>
+          <t>278253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453828</t>
+          <t>452291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>527431</t>
+          <t>525942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414789</t>
+          <t>415619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467790</t>
+          <t>464060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429740</t>
+          <t>428776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481280</t>
+          <t>482368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>858479</t>
+          <t>859968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932082</t>
+          <t>933619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182843</t>
+          <t>182432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232201</t>
+          <t>234066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182122</t>
+          <t>181576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236259</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377123</t>
+          <t>379254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>447554</t>
+          <t>452198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382416</t>
+          <t>380551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>431774</t>
+          <t>432185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>380117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>431777</t>
+          <t>432323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>780962</t>
+          <t>776318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>851393</t>
+          <t>849262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109915</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150474</t>
+          <t>149672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111104</t>
+          <t>111112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150595</t>
+          <t>150369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232714</t>
+          <t>228953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>287951</t>
+          <t>282860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274393</t>
+          <t>275195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314952</t>
+          <t>315776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>291822</t>
+          <t>292048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>331313</t>
+          <t>331305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579333</t>
+          <t>584424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>634570</t>
+          <t>638331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>54884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87283</t>
+          <t>85955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79021</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112143</t>
+          <t>113544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140950</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189370</t>
+          <t>189821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218262</t>
+          <t>219590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249823</t>
+          <t>250661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240864</t>
+          <t>239463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273986</t>
+          <t>274012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>469182</t>
+          <t>468731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517602</t>
+          <t>515535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83960</t>
+          <t>82274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>102679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140227</t>
+          <t>139133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165019</t>
+          <t>166837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214047</t>
+          <t>216567</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164829</t>
+          <t>166515</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195724</t>
+          <t>196484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246587</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>283817</t>
+          <t>284135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>421556</t>
+          <t>419036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>470584</t>
+          <t>468766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>992066</t>
+          <t>988394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1098336</t>
+          <t>1099963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,82 +6128,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1119928</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1059267</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1179250</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2163863</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2087027</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2239782</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>32,22%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1119928</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1061306</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1178750</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2163863</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>2081858</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2243353</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2310809</t>
+          <t>2309182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2417079</t>
+          <t>2420751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,82 +6241,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>67,73%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2422794</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2363472</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2483455</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>68,39%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>70,1%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>4788004</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>4712085</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4864840</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>67,78%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2422794</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2363972</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2481416</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>68,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>4468</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>4788004</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>4708514</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4870009</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103511</t>
+          <t>102980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139879</t>
+          <t>140030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92506</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126189</t>
+          <t>129470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208424</t>
+          <t>208289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258279</t>
+          <t>260011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274002</t>
+          <t>273851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310370</t>
+          <t>310901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266786</t>
+          <t>263505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300469</t>
+          <t>299786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>548577</t>
+          <t>546845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598432</t>
+          <t>598567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182544</t>
+          <t>180868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230064</t>
+          <t>229627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158257</t>
+          <t>159956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201661</t>
+          <t>201820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355811</t>
+          <t>355518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415841</t>
+          <t>417640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360432</t>
+          <t>360869</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407952</t>
+          <t>409628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359894</t>
+          <t>359735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403298</t>
+          <t>401599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736211</t>
+          <t>734412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796241</t>
+          <t>796534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191374</t>
+          <t>194753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242285</t>
+          <t>243689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219400</t>
+          <t>221130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>266516</t>
+          <t>270233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>425627</t>
+          <t>424189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494940</t>
+          <t>494505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423859</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474770</t>
+          <t>471391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391377</t>
+          <t>387660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>438493</t>
+          <t>436763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>829097</t>
+          <t>829532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>898410</t>
+          <t>899848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224676</t>
+          <t>223856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275473</t>
+          <t>274898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>247531</t>
+          <t>250528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301587</t>
+          <t>303759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491410</t>
+          <t>485263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564664</t>
+          <t>564875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366611</t>
+          <t>367186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>417408</t>
+          <t>418228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346405</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400461</t>
+          <t>397464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725412</t>
+          <t>725201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>798666</t>
+          <t>804813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146423</t>
+          <t>146847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188684</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166236</t>
+          <t>165838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>212130</t>
+          <t>214366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324719</t>
+          <t>324162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>383727</t>
+          <t>387609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286059</t>
+          <t>285207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328320</t>
+          <t>327896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>282423</t>
+          <t>280187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328317</t>
+          <t>328715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>585569</t>
+          <t>581687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>644577</t>
+          <t>645134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78171</t>
+          <t>79227</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110903</t>
+          <t>111617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102331</t>
+          <t>101660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>137273</t>
+          <t>137635</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>188807</t>
+          <t>188607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238062</t>
+          <t>239068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214568</t>
+          <t>213854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247300</t>
+          <t>246244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236855</t>
+          <t>236493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271797</t>
+          <t>272468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461537</t>
+          <t>460531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510792</t>
+          <t>510992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85775</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119037</t>
+          <t>121043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188644</t>
+          <t>191255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>240465</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168688</t>
+          <t>169123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195153</t>
+          <t>195806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>234702</t>
+          <t>235567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278659</t>
+          <t>276653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413330</t>
+          <t>411694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463515</t>
+          <t>460904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1075363</t>
+          <t>1069847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1183427</t>
+          <t>1184093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1203999</t>
+          <t>1198004</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1316227</t>
+          <t>1315886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2308918</t>
+          <t>2314822</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2472259</t>
+          <t>2470344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2183855</t>
+          <t>2183189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2291919</t>
+          <t>2297435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2210565</t>
+          <t>2210906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2322793</t>
+          <t>2328788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4421816</t>
+          <t>4423731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4585157</t>
+          <t>4579253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75599</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>40309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79089</t>
+          <t>80264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80367</t>
+          <t>81650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138891</t>
+          <t>137298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306693</t>
+          <t>309284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350198</t>
+          <t>350319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231212</t>
+          <t>230037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269465</t>
+          <t>269992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553703</t>
+          <t>555296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612227</t>
+          <t>610944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>74053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71515</t>
+          <t>72023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263386</t>
+          <t>280836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125065</t>
+          <t>124947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355742</t>
+          <t>362625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346694</t>
+          <t>347005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381052</t>
+          <t>380957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>240812</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432683</t>
+          <t>432175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569514</t>
+          <t>562631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800191</t>
+          <t>800309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87558</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94531</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124516</t>
+          <t>124853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174630</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>447261</t>
+          <t>446307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477556</t>
+          <t>476001</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495349</t>
+          <t>495330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532807</t>
+          <t>531452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>950070</t>
+          <t>952093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1000184</t>
+          <t>999847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119837</t>
+          <t>122315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83322</t>
+          <t>82802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>116712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110736</t>
+          <t>108842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222934</t>
+          <t>221488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>759770</t>
+          <t>757292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841567</t>
+          <t>843423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561495</t>
+          <t>560089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593479</t>
+          <t>593999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1333474</t>
+          <t>1334920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1445672</t>
+          <t>1447566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79339</t>
+          <t>78224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112902</t>
+          <t>112148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94216</t>
+          <t>95078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122668</t>
+          <t>122693</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182425</t>
+          <t>181838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224352</t>
+          <t>226574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439314</t>
+          <t>440068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472877</t>
+          <t>473992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417434</t>
+          <t>417409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445886</t>
+          <t>445024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>867967</t>
+          <t>865745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909894</t>
+          <t>910481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>27651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77941</t>
+          <t>77275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>44686</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111646</t>
+          <t>114330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319064</t>
+          <t>319410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>338166</t>
+          <t>337538</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>526763</t>
+          <t>527429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588302</t>
+          <t>588414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>858247</t>
+          <t>855563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>929126</t>
+          <t>925207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68754</t>
+          <t>69526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92796</t>
+          <t>92184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>92553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120677</t>
+          <t>120037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248514</t>
+          <t>246141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263160</t>
+          <t>262903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324939</t>
+          <t>325551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>348209</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>577779</t>
+          <t>578419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606602</t>
+          <t>605903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>329674</t>
+          <t>317457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>465813</t>
+          <t>466090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>518264</t>
+          <t>504971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>809900</t>
+          <t>788405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>904865</t>
+          <t>894116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1231268</t>
+          <t>1219741</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2950090</t>
+          <t>2949813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3086229</t>
+          <t>3098446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2833822</t>
+          <t>2855317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3125458</t>
+          <t>3138751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5828357</t>
+          <t>5839884</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6154760</t>
+          <t>6165509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80678</t>
+          <t>80823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82294</t>
+          <t>80448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115515</t>
+          <t>114091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141629</t>
+          <t>140761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187102</t>
+          <t>186681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405143</t>
+          <t>404998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434068</t>
+          <t>436801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344512</t>
+          <t>345936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>377733</t>
+          <t>379579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758746</t>
+          <t>759167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>804219</t>
+          <t>805087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105270</t>
+          <t>105769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>148325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110700</t>
+          <t>110429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152209</t>
+          <t>152921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226153</t>
+          <t>226056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287009</t>
+          <t>285458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586779</t>
+          <t>583338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>626393</t>
+          <t>625894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461571</t>
+          <t>460859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503080</t>
+          <t>503351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1058434</t>
+          <t>1059985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1119290</t>
+          <t>1119387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113328</t>
+          <t>114584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150654</t>
+          <t>151460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195683</t>
+          <t>197141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238207</t>
+          <t>240163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298620</t>
+          <t>302563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521806</t>
+          <t>520550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557798</t>
+          <t>558605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482044</t>
+          <t>480586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527073</t>
+          <t>526267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1014241</t>
+          <t>1010298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074654</t>
+          <t>1072698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>67293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100692</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>114454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154020</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192279</t>
+          <t>188595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242044</t>
+          <t>242492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415565</t>
+          <t>415341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450729</t>
+          <t>448964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351400</t>
+          <t>352181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391280</t>
+          <t>390966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779633</t>
+          <t>779185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>829398</t>
+          <t>833082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>73184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96410</t>
+          <t>98437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132277</t>
+          <t>135130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176744</t>
+          <t>178006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225179</t>
+          <t>228609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271821</t>
+          <t>271025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303303</t>
+          <t>302966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264626</t>
+          <t>261773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>298466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>547874</t>
+          <t>544444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>596309</t>
+          <t>595047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54239</t>
+          <t>52653</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82633</t>
+          <t>80354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119062</t>
+          <t>118718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151768</t>
+          <t>150124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>180606</t>
+          <t>179942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224003</t>
+          <t>224216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200129</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228523</t>
+          <t>230109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180338</t>
+          <t>181982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213044</t>
+          <t>213388</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>390865</t>
+          <t>390652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>434262</t>
+          <t>434926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50446</t>
+          <t>50484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76793</t>
+          <t>76831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119527</t>
+          <t>117174</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>156022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179893</t>
+          <t>178735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223629</t>
+          <t>224609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>126211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152596</t>
+          <t>152558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173276</t>
+          <t>172983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>209478</t>
+          <t>211831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308419</t>
+          <t>307439</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>352155</t>
+          <t>353313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2603359</t>
+          <t>2602688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2687893</t>
+          <t>2691077</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2336996</t>
+          <t>2340413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2441239</t>
+          <t>2442446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4968419</t>
+          <t>4967304</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5102619</t>
+          <t>5105472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109456</t>
+          <t>110862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149136</t>
+          <t>148251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93575</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130031</t>
+          <t>128761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215174</t>
+          <t>211590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267511</t>
+          <t>268989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302117</t>
+          <t>303002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>340391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299269</t>
+          <t>300539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335725</t>
+          <t>337037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>613042</t>
+          <t>611564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>665379</t>
+          <t>668963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181749</t>
+          <t>180740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229818</t>
+          <t>229786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183140</t>
+          <t>182491</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232414</t>
+          <t>229657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>374685</t>
+          <t>376495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442962</t>
+          <t>446427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455375</t>
+          <t>455407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503444</t>
+          <t>504453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>380598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427115</t>
+          <t>427764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>852487</t>
+          <t>849022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920764</t>
+          <t>918954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214822</t>
+          <t>211738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>263263</t>
+          <t>263902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224661</t>
+          <t>228546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>278253</t>
+          <t>277990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452291</t>
+          <t>450610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525942</t>
+          <t>526794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415619</t>
+          <t>414980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464060</t>
+          <t>467144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>428776</t>
+          <t>429039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482368</t>
+          <t>478483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>859968</t>
+          <t>859116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933619</t>
+          <t>935300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182432</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234066</t>
+          <t>231064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181576</t>
+          <t>184830</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233782</t>
+          <t>232764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379254</t>
+          <t>379973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>452198</t>
+          <t>453062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>380551</t>
+          <t>383553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432185</t>
+          <t>431422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>380117</t>
+          <t>381135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>432323</t>
+          <t>429069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>776318</t>
+          <t>775454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>849262</t>
+          <t>848543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109091</t>
+          <t>107891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149672</t>
+          <t>146184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111112</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150369</t>
+          <t>151967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228953</t>
+          <t>230256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282860</t>
+          <t>286868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275195</t>
+          <t>278683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>315776</t>
+          <t>316976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>292048</t>
+          <t>290450</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>331305</t>
+          <t>331657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>584424</t>
+          <t>580416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>638331</t>
+          <t>637028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54884</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85955</t>
+          <t>85381</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78995</t>
+          <t>79631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113544</t>
+          <t>114089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143017</t>
+          <t>142476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189821</t>
+          <t>188829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219590</t>
+          <t>220164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250661</t>
+          <t>250922</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239463</t>
+          <t>238918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274012</t>
+          <t>273376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>468731</t>
+          <t>469723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515535</t>
+          <t>516076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52305</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82274</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102679</t>
+          <t>102343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139133</t>
+          <t>139332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166837</t>
+          <t>164165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216567</t>
+          <t>212607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166515</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>196484</t>
+          <t>195947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>247482</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>284471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419036</t>
+          <t>422996</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>468766</t>
+          <t>471438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>988394</t>
+          <t>989070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1099963</t>
+          <t>1096750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1059267</t>
+          <t>1061488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1179250</t>
+          <t>1178397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2087027</t>
+          <t>2084308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2239782</t>
+          <t>2246181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2309182</t>
+          <t>2312395</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2420751</t>
+          <t>2420075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2363472</t>
+          <t>2364325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2483455</t>
+          <t>2481234</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4712085</t>
+          <t>4705686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4864840</t>
+          <t>4867559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102980</t>
+          <t>102222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140030</t>
+          <t>141171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93189</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129470</t>
+          <t>126528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208289</t>
+          <t>206668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260011</t>
+          <t>257141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273851</t>
+          <t>272710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310901</t>
+          <t>311659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263505</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299786</t>
+          <t>299998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546845</t>
+          <t>549715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598567</t>
+          <t>600188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180868</t>
+          <t>183648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229627</t>
+          <t>229934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159956</t>
+          <t>159666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201820</t>
+          <t>204006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355518</t>
+          <t>356656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417640</t>
+          <t>421015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360869</t>
+          <t>360562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409628</t>
+          <t>406848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359735</t>
+          <t>357549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401599</t>
+          <t>401889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734412</t>
+          <t>731037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796534</t>
+          <t>795396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194753</t>
+          <t>193540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243689</t>
+          <t>241423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>221130</t>
+          <t>220037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270233</t>
+          <t>269976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>424189</t>
+          <t>427485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494505</t>
+          <t>495975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422455</t>
+          <t>424721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471391</t>
+          <t>472604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>387660</t>
+          <t>387917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>436763</t>
+          <t>437856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>829532</t>
+          <t>828062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>899848</t>
+          <t>896552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223856</t>
+          <t>224236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274898</t>
+          <t>273841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250528</t>
+          <t>250260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>302044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485263</t>
+          <t>487572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564875</t>
+          <t>559172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367186</t>
+          <t>368243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>418228</t>
+          <t>417848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>345948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397464</t>
+          <t>397732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725201</t>
+          <t>730904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>804813</t>
+          <t>802504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146847</t>
+          <t>145277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189536</t>
+          <t>189273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165838</t>
+          <t>162572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214366</t>
+          <t>211157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324162</t>
+          <t>323082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387609</t>
+          <t>390169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>285207</t>
+          <t>285470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327896</t>
+          <t>329466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>280187</t>
+          <t>283396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328715</t>
+          <t>331981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>581687</t>
+          <t>579127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>645134</t>
+          <t>646214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79227</t>
+          <t>79239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111617</t>
+          <t>114054</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101660</t>
+          <t>101761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>137635</t>
+          <t>136497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>188607</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239068</t>
+          <t>238424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213854</t>
+          <t>211417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246244</t>
+          <t>246232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236493</t>
+          <t>237631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272468</t>
+          <t>272367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460531</t>
+          <t>461175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510992</t>
+          <t>507481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58657</t>
+          <t>59467</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121043</t>
+          <t>120302</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162129</t>
+          <t>162683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191255</t>
+          <t>190253</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240465</t>
+          <t>240198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169123</t>
+          <t>170158</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195806</t>
+          <t>194996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>235567</t>
+          <t>235013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>276653</t>
+          <t>277394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>411694</t>
+          <t>411961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>460904</t>
+          <t>461906</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1069847</t>
+          <t>1072306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1184093</t>
+          <t>1181665</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1198004</t>
+          <t>1201964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1315886</t>
+          <t>1319856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2314822</t>
+          <t>2305668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2470344</t>
+          <t>2468465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2183189</t>
+          <t>2185617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2297435</t>
+          <t>2294976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2210906</t>
+          <t>2206936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2328788</t>
+          <t>2324828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4423731</t>
+          <t>4425610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4579253</t>
+          <t>4588407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>63250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>41305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>89498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80264</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>107788</t>
+          <t>129564</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81650</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>162261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>332314</t>
+          <t>327269</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309284</t>
+          <t>301021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350319</t>
+          <t>349214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252491</t>
+          <t>293254</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230037</t>
+          <t>269058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269992</t>
+          <t>311628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>584806</t>
+          <t>620523</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555296</t>
+          <t>587826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610944</t>
+          <t>649380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>382292</t>
+          <t>390519</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>382292</t>
+          <t>390519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>382292</t>
+          <t>390519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310301</t>
+          <t>359568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310301</t>
+          <t>359568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310301</t>
+          <t>359568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>692594</t>
+          <t>750087</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>692594</t>
+          <t>750087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>692594</t>
+          <t>750087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>49193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74053</t>
+          <t>86869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136342</t>
+          <t>85349</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>67499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280836</t>
+          <t>105621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>191783</t>
+          <t>150684</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124947</t>
+          <t>125814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>362625</t>
+          <t>177383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>365617</t>
+          <t>409075</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347005</t>
+          <t>387541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380957</t>
+          <t>425217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>367856</t>
+          <t>406024</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223362</t>
+          <t>385752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432175</t>
+          <t>423874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>733473</t>
+          <t>815099</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562631</t>
+          <t>788400</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800309</t>
+          <t>839969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421058</t>
+          <t>474410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421058</t>
+          <t>474410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>421058</t>
+          <t>474410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504198</t>
+          <t>491373</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>504198</t>
+          <t>491373</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>504198</t>
+          <t>491373</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>925256</t>
+          <t>965783</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>925256</t>
+          <t>965783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>925256</t>
+          <t>965783</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72824</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58818</t>
+          <t>79320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88512</t>
+          <t>117762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>95290</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58428</t>
+          <t>81281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94550</t>
+          <t>111095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>151490</t>
+          <t>193941</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124853</t>
+          <t>170034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172607</t>
+          <t>218094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>461995</t>
+          <t>516707</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446307</t>
+          <t>497596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476001</t>
+          <t>536038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511214</t>
+          <t>525180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495330</t>
+          <t>509375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531452</t>
+          <t>539189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>973210</t>
+          <t>1041887</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>952093</t>
+          <t>1017734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999847</t>
+          <t>1065794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>534819</t>
+          <t>615358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534819</t>
+          <t>615358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>534819</t>
+          <t>615358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>589880</t>
+          <t>620470</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>589880</t>
+          <t>620470</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>589880</t>
+          <t>620470</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1124700</t>
+          <t>1235828</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124700</t>
+          <t>1235828</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1124700</t>
+          <t>1235828</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>97097</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>79290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>118053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>111691</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82802</t>
+          <t>95361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116712</t>
+          <t>127182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>178369</t>
+          <t>208788</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108842</t>
+          <t>185619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221488</t>
+          <t>234449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>799014</t>
+          <t>593901</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>757292</t>
+          <t>572945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843423</t>
+          <t>611708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>579025</t>
+          <t>621346</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>560089</t>
+          <t>605855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593999</t>
+          <t>637676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1378039</t>
+          <t>1215247</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1334920</t>
+          <t>1189586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1447566</t>
+          <t>1238416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>879607</t>
+          <t>690998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879607</t>
+          <t>690998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>879607</t>
+          <t>690998</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>676801</t>
+          <t>733037</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>676801</t>
+          <t>733037</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>676801</t>
+          <t>733037</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1556408</t>
+          <t>1424035</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1556408</t>
+          <t>1424035</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1556408</t>
+          <t>1424035</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95138</t>
+          <t>107129</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78224</t>
+          <t>89814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112148</t>
+          <t>129128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95078</t>
+          <t>107324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122693</t>
+          <t>138348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>202910</t>
+          <t>229052</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181838</t>
+          <t>205679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226574</t>
+          <t>252637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>457078</t>
+          <t>491243</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440068</t>
+          <t>469244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473992</t>
+          <t>508558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>432330</t>
+          <t>480381</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417409</t>
+          <t>463956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445024</t>
+          <t>494980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>889409</t>
+          <t>971623</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865745</t>
+          <t>948038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910481</t>
+          <t>994996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>552216</t>
+          <t>598372</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>552216</t>
+          <t>598372</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>552216</t>
+          <t>598372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540102</t>
+          <t>602304</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540102</t>
+          <t>602304</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540102</t>
+          <t>602304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1092319</t>
+          <t>1200675</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1092319</t>
+          <t>1200675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1092319</t>
+          <t>1200675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>40673</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45779</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>93904</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44686</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114330</t>
+          <t>107631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>329400</t>
+          <t>363071</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319410</t>
+          <t>353163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337538</t>
+          <t>372057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>556306</t>
+          <t>381382</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>527429</t>
+          <t>371182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588414</t>
+          <t>390874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>885706</t>
+          <t>744454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>855563</t>
+          <t>730727</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>925207</t>
+          <t>758372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365189</t>
+          <t>403744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365189</t>
+          <t>403744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365189</t>
+          <t>403744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>604704</t>
+          <t>434613</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>604704</t>
+          <t>434613</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>604704</t>
+          <t>434613</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>969893</t>
+          <t>838358</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>969893</t>
+          <t>838358</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>969893</t>
+          <t>838358</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>80804</t>
+          <t>89782</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>77434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>102526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>105439</t>
+          <t>116386</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92553</t>
+          <t>101653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120037</t>
+          <t>130305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>256086</t>
+          <t>281280</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246141</t>
+          <t>271912</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262903</t>
+          <t>288905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>336931</t>
+          <t>366269</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325551</t>
+          <t>353525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348209</t>
+          <t>378617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>593017</t>
+          <t>647549</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578419</t>
+          <t>633630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>605903</t>
+          <t>662282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280721</t>
+          <t>307884</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280721</t>
+          <t>307884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>280721</t>
+          <t>307884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417735</t>
+          <t>456051</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417735</t>
+          <t>456051</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>417735</t>
+          <t>456051</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>698456</t>
+          <t>763935</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>698456</t>
+          <t>763935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>698456</t>
+          <t>763935</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>317457</t>
+          <t>452722</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>466090</t>
+          <t>545741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>504971</t>
+          <t>581647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>788405</t>
+          <t>665420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>894116</t>
+          <t>1057634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1219741</t>
+          <t>1186356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3001505</t>
+          <t>2982545</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2949813</t>
+          <t>2935543</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3098446</t>
+          <t>3028562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3036154</t>
+          <t>3073836</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2855317</t>
+          <t>3031996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3138751</t>
+          <t>3115769</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6037659</t>
+          <t>6056381</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5839884</t>
+          <t>5992345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6165509</t>
+          <t>6121067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
